--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -896,22 +896,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -896,22 +896,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -896,22 +896,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -896,22 +896,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -896,22 +896,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -997,22 +997,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -896,22 +896,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -997,22 +997,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1464,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -896,22 +896,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1363,10 +1363,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1464,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -997,22 +997,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1363,10 +1363,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1464,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,55 +528,85 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -679,7 +709,25 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>45975.39583333334</v>
       </c>
     </row>
@@ -780,7 +828,25 @@
       <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>45975.41666666666</v>
       </c>
     </row>
@@ -881,7 +947,25 @@
       <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" s="3" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>45975.64583333334</v>
       </c>
     </row>
@@ -982,7 +1066,25 @@
       <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" s="3" t="n">
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>45975.6875</v>
       </c>
     </row>
@@ -1083,7 +1185,25 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" s="3" t="n">
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>45975.6875</v>
       </c>
     </row>
@@ -1184,7 +1304,25 @@
       <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" s="3" t="n">
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>45975.6875</v>
       </c>
     </row>
@@ -1285,7 +1423,25 @@
       <c r="AB8" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
       </c>
     </row>
@@ -1386,7 +1542,25 @@
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" s="3" t="n">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>45975.69791666666</v>
       </c>
     </row>
@@ -1464,30 +1638,48 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.8</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AB10" t="n">
         <v>1.9</v>
       </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="3" t="n">
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
         <v>45975.69791666666</v>
       </c>
     </row>
@@ -1588,7 +1780,25 @@
       <c r="AB11" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="3" t="n">
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
         <v>45975.83333333334</v>
       </c>
     </row>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -980,22 +980,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -980,22 +980,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -980,22 +980,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>45975.39583333334</v>
+        <v>45975.375</v>
       </c>
     </row>
     <row r="3">
@@ -737,7 +737,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45975.41666666666</v>
+        <v>45975.39583333334</v>
       </c>
     </row>
     <row r="4">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>45975.64583333334</v>
+        <v>45975.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -975,27 +975,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>45975.6875</v>
+        <v>45975.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>45975.6875</v>
+        <v>45975.64583333334</v>
       </c>
     </row>
     <row r="7">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>45975.69791666666</v>
+        <v>45975.6875</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45975.69791666666</v>
+        <v>45975.6875</v>
       </c>
     </row>
     <row r="11">
@@ -1689,116 +1689,354 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Northern Ireland NIFL Premiership</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Coleraine</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>45975.69791666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Northern Ireland NIFL Premiership</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Glentoran</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Carrick Rangers</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>45975.69791666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>2.12</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M13" t="n">
         <v>3.35</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N13" t="n">
         <v>3.4</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.18</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AB13" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="3" t="n">
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>
       </c>
     </row>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1968,14 +1968,14 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.35</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
         <v>1.62</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="O8" t="n">
         <v>2.94</v>
@@ -1412,16 +1412,16 @@
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
         <v>4.25</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1977,40 +1977,40 @@
         <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
         <v>2.12</v>
@@ -2019,22 +2019,22 @@
         <v>1.64</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1570,27 +1570,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45975.6875</v>
+        <v>45975.69791666666</v>
       </c>
     </row>
     <row r="11">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,194 +1849,75 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.07</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>2.98</v>
       </c>
       <c r="O12" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
         <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.22</v>
+        <v>1.46</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45975.69791666666</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Paysandu</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>
       </c>
     </row>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>2.95</v>
@@ -1272,10 +1272,10 @@
         <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
         <v>3.4</v>
@@ -1293,22 +1293,22 @@
         <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1739,19 +1739,19 @@
         <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>5.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="T11" t="n">
         <v>2.71</v>
@@ -1763,10 +1763,10 @@
         <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.21</v>
@@ -1787,10 +1787,10 @@
         <v>1.32</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.88</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
         <v>1.18</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.18</v>
+        <v>2.89</v>
       </c>
       <c r="M12" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="N12" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>3.13</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
         <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
         <v>1.31</v>
       </c>
       <c r="V12" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.01</v>
@@ -1888,34 +1888,34 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
         <v>2.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD12" t="n">
         <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF12" t="n">
         <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45975.39583333334</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45975.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>12.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.56</v>
+        <v>1.71</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.99</v>
+        <v>10.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="T8" t="n">
-        <v>3.14</v>
+        <v>2.53</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.01</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.96</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>12.4</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.71</v>
+        <v>2.56</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.5</v>
+        <v>4.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>2.53</v>
+        <v>3.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>5.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>3.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
         <v>2.21</v>
@@ -1748,22 +1748,22 @@
         <v>5.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="T11" t="n">
         <v>2.71</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
         <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC11" t="n">
         <v>2.88</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>1.75</v>
       </c>
       <c r="P7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.62</v>
+        <v>3.42</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45975.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>3.07</v>
       </c>
       <c r="N8" t="n">
-        <v>12.4</v>
+        <v>3.32</v>
       </c>
       <c r="O8" t="n">
-        <v>1.71</v>
+        <v>2.97</v>
       </c>
       <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.32</v>
       </c>
-      <c r="Q8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T8" t="n">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.74</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.5</v>
+        <v>1.64</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.99</v>
+        <v>4.8</v>
       </c>
       <c r="R9" t="n">
         <v>1.45</v>
@@ -1522,7 +1522,7 @@
         <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
@@ -1537,13 +1537,13 @@
         <v>2.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
         <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
         <v>1.17</v>
@@ -1552,13 +1552,13 @@
         <v>1.93</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1849,25 +1849,25 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
         <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>3.39</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.13</v>
+        <v>2.78</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
         <v>2.62</v>
@@ -1876,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
         <v>8.5</v>
@@ -1891,7 +1891,7 @@
         <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="AA12" t="n">
         <v>2.16</v>
@@ -1906,16 +1906,16 @@
         <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
         <v>1.55</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4.8</v>
       </c>
-      <c r="N7" t="n">
-        <v>14</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>11.6</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.42</v>
+        <v>1.76</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45975.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.07</v>
+        <v>4.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3.32</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
-        <v>2.97</v>
+        <v>1.75</v>
       </c>
       <c r="P8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AC8" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.64</v>
+        <v>2.9</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.54</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
         <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="O12" t="n">
         <v>3.39</v>
       </c>
       <c r="P12" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
         <v>2.78</v>
@@ -1870,19 +1870,19 @@
         <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
         <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1894,13 +1894,13 @@
         <v>3.01</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
         <v>1.22</v>
@@ -1909,10 +1909,10 @@
         <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
         <v>1.34</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O3" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
         <v>3.34</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>2.43</v>
@@ -942,7 +942,7 @@
         <v>2.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="AB4" t="n">
         <v>1.54</v>
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="R7" t="n">
         <v>1.45</v>
@@ -1296,13 +1296,13 @@
         <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
         <v>3.98</v>
@@ -1311,16 +1311,16 @@
         <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45975.6875</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="N8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.75</v>
@@ -1391,10 +1391,10 @@
         <v>11.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
         <v>2.67</v>
@@ -1403,7 +1403,7 @@
         <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
@@ -1418,10 +1418,10 @@
         <v>3.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
         <v>3.1</v>
@@ -1430,16 +1430,16 @@
         <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
         <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>2.48</v>
@@ -1299,10 +1299,10 @@
         <v>2.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" t="n">
         <v>3.98</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
         <v>1.75</v>
@@ -1418,10 +1418,10 @@
         <v>3.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>3.1</v>
@@ -1504,16 +1504,16 @@
         <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
         <v>3.3</v>
@@ -1522,7 +1522,7 @@
         <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
@@ -1543,7 +1543,7 @@
         <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1.15</v>
@@ -1558,7 +1558,7 @@
         <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1650,7 +1650,7 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
         <v>3.58</v>
@@ -1677,7 +1677,7 @@
         <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1858,16 +1858,16 @@
         <v>2.98</v>
       </c>
       <c r="O12" t="n">
-        <v>3.39</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
         <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
         <v>2.59</v>
@@ -1879,13 +1879,13 @@
         <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.38</v>
@@ -1903,10 +1903,10 @@
         <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF12" t="n">
         <v>1.86</v>
@@ -1915,7 +1915,7 @@
         <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -778,37 +778,37 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="N3" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
         <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V3" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
         <v>1.03</v>
@@ -817,34 +817,34 @@
         <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45975.39583333334</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.71</v>
+        <v>4.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="T4" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45975.41666666666</v>
@@ -1016,67 +1016,67 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1144,64 +1144,64 @@
         <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB6" t="n">
         <v>1.89</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45975.64583333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>12.7</v>
       </c>
       <c r="O7" t="n">
-        <v>2.48</v>
+        <v>1.74</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.25</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="T7" t="n">
-        <v>3.14</v>
+        <v>2.67</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>8.800000000000001</v>
+        <v>6.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.98</v>
+        <v>2.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>2.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.79</v>
+        <v>3.42</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45975.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>14</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.75</v>
+        <v>2.97</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.6</v>
+        <v>4.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>2.67</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.06</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.28</v>
+        <v>2.51</v>
       </c>
       <c r="AA8" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.42</v>
+        <v>1.62</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AB9" t="n">
         <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>5.21</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
@@ -1656,16 +1656,16 @@
         <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
         <v>1.81</v>
@@ -1674,10 +1674,10 @@
         <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.98</v>
+        <v>2.35</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.39</v>
       </c>
       <c r="P12" t="n">
         <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
         <v>2.59</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="U12" t="n">
         <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>1.01</v>
@@ -1888,16 +1888,16 @@
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
         <v>3.01</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
         <v>4</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45975.41666666666</v>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.31</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.02</v>
+        <v>2.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.92</v>
+        <v>4.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U5" t="n">
         <v>1.29</v>
       </c>
       <c r="V5" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AD5" t="n">
         <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>45975.54166666666</v>
+        <v>45975.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
         <v>2.5</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.6</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.42</v>
-      </c>
       <c r="AA6" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>45975.64583333334</v>
+        <v>45975.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,52 +1254,52 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>12.7</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>4.16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AB7" t="n">
         <v>1.87</v>
@@ -1311,19 +1311,19 @@
         <v>1.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.57</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.42</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45975.6875</v>
+        <v>45975.64583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1492,40 +1492,40 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T9" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
@@ -1534,31 +1534,31 @@
         <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
         <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="AD9" t="n">
         <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
         <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.58</v>
+        <v>11.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="T10" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>6.2</v>
+        <v>5.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.01</v>
+        <v>2.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.81</v>
+        <v>2.56</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45975.69791666666</v>
+        <v>45975.6875</v>
       </c>
     </row>
     <row r="11">
@@ -1808,116 +1808,235 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Northern Ireland NIFL Premiership</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Glentoran</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Carrick Rangers</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>45975.69791666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>3.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M13" t="n">
         <v>3.1</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N13" t="n">
         <v>2.35</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O13" t="n">
         <v>3.39</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P13" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q13" t="n">
         <v>2.78</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>1.43</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S13" t="n">
         <v>2.59</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>3.23</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>1.32</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V13" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="W12" t="n">
+      <c r="W13" t="n">
         <v>1.01</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X13" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y13" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z13" t="n">
         <v>3.01</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA13" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AB13" t="n">
         <v>1.66</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AC13" t="n">
         <v>4</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AD13" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AE13" t="n">
         <v>1.84</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AF13" t="n">
         <v>1.86</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AG13" t="n">
         <v>1.31</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AH13" t="n">
         <v>1.35</v>
       </c>
-      <c r="AI12" s="3" t="n">
+      <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>
       </c>
     </row>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>2.97</v>
+        <v>1.69</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.34</v>
+        <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>2.49</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>8.4</v>
+        <v>5.95</v>
       </c>
       <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.01</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.51</v>
+        <v>3.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.51</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.99</v>
+        <v>2.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.62</v>
+        <v>3.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.07</v>
       </c>
       <c r="N10" t="n">
-        <v>9.800000000000001</v>
+        <v>3.32</v>
       </c>
       <c r="O10" t="n">
-        <v>1.69</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="T10" t="n">
-        <v>2.49</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>5.95</v>
+        <v>8.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.42</v>
+        <v>2.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.56</v>
+        <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.8</v>
+        <v>1.56</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.6875</v>
@@ -1849,31 +1849,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.58</v>
+        <v>5.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
         <v>2.91</v>
       </c>
       <c r="T12" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
         <v>1.41</v>
@@ -1882,37 +1882,37 @@
         <v>6.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>3.01</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
         <v>2.22</v>
@@ -1968,40 +1968,40 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.1</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.23</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
@@ -2010,31 +2010,31 @@
         <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC13" t="n">
         <v>4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
         <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -778,40 +778,40 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.62</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.59</v>
-      </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U3" t="n">
         <v>1.24</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.07</v>
@@ -838,13 +838,13 @@
         <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45975.39583333334</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="P5" t="n">
         <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
         <v>1.44</v>
@@ -1040,10 +1040,10 @@
         <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U5" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="V5" t="n">
         <v>10</v>
@@ -1055,16 +1055,16 @@
         <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
         <v>4.45</v>
@@ -1073,16 +1073,16 @@
         <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45975.41666666666</v>
@@ -1263,40 +1263,40 @@
         <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.16</v>
+        <v>4.07</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="AA7" t="n">
         <v>1.83</v>
@@ -1305,10 +1305,10 @@
         <v>1.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
         <v>1.73</v>
@@ -1317,10 +1317,10 @@
         <v>2.03</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45975.64583333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>9.800000000000001</v>
+        <v>3.18</v>
       </c>
       <c r="O8" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.5</v>
+        <v>4.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>5.95</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.42</v>
+        <v>2.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.78</v>
+        <v>4.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.56</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.8</v>
+        <v>1.67</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>2.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.12</v>
+        <v>11.32</v>
       </c>
       <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.44</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V9" t="n">
-        <v>9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.56</v>
+        <v>4.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1623,7 +1623,7 @@
         <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
         <v>3.95</v>
@@ -1632,10 +1632,10 @@
         <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
         <v>1.27</v>
@@ -1668,16 +1668,16 @@
         <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.6875</v>
@@ -1867,28 +1867,28 @@
         <v>5.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
         <v>3.55</v>
@@ -1903,19 +1903,19 @@
         <v>3.01</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1980,28 +1980,28 @@
         <v>3.84</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
         <v>2.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
@@ -2019,10 +2019,10 @@
         <v>1.64</v>
       </c>
       <c r="AC13" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
         <v>1.86</v>
@@ -2031,10 +2031,10 @@
         <v>1.82</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.34</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45975.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45975.41666666666</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45975.54166666666</v>
@@ -1373,40 +1373,40 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.48</v>
+        <v>2.93</v>
       </c>
       <c r="P8" t="n">
         <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
         <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
@@ -1418,28 +1418,28 @@
         <v>2.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>9.800000000000001</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.43</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.32</v>
+        <v>3.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>2.39</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>5.35</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>2.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.46</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.97</v>
+        <v>2.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="M10" t="n">
-        <v>3.07</v>
+        <v>6.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.32</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.95</v>
+        <v>10.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>2.34</v>
+        <v>2.83</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="V10" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.5</v>
+        <v>2.49</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.6875</v>
@@ -1968,40 +1968,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="P13" t="n">
         <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R13" t="n">
         <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="T13" t="n">
         <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
@@ -2013,10 +2013,10 @@
         <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
         <v>3.84</v>
@@ -2028,13 +2028,13 @@
         <v>1.86</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1052,37 +1052,37 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45975.41666666666</v>
@@ -1138,25 +1138,25 @@
         <v>2.18</v>
       </c>
       <c r="M6" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="P6" t="n">
         <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="T6" t="n">
         <v>3.28</v>
@@ -1174,28 +1174,28 @@
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD6" t="n">
         <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
         <v>1.28</v>
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="O7" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="P7" t="n">
         <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="R7" t="n">
         <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="T7" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
         <v>7.1</v>
@@ -1296,13 +1296,13 @@
         <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>3.08</v>
@@ -1311,16 +1311,16 @@
         <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45975.64583333334</v>
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="O8" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.14</v>
+        <v>4.29</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
@@ -1415,31 +1415,31 @@
         <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1504,7 +1504,7 @@
         <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
         <v>3.95</v>
@@ -1516,7 +1516,7 @@
         <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
         <v>1.27</v>
@@ -1528,13 +1528,13 @@
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
         <v>1.49</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AA9" t="n">
         <v>2.58</v>
@@ -1543,7 +1543,7 @@
         <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>4.91</v>
       </c>
       <c r="AD9" t="n">
         <v>1.18</v>
@@ -1552,13 +1552,13 @@
         <v>2.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1614,19 +1614,19 @@
         <v>1.17</v>
       </c>
       <c r="M10" t="n">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>12.16</v>
       </c>
       <c r="O10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.08</v>
+        <v>10.33</v>
       </c>
       <c r="R10" t="n">
         <v>1.34</v>
@@ -1635,16 +1635,16 @@
         <v>2.83</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA10" t="n">
         <v>1.65</v>
@@ -1662,10 +1662,10 @@
         <v>2.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE10" t="n">
         <v>2.6</v>
@@ -1674,10 +1674,10 @@
         <v>1.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.6875</v>
@@ -1861,22 +1861,22 @@
         <v>2.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="Q12" t="n">
         <v>5.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="T12" t="n">
         <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
         <v>6</v>
@@ -1888,10 +1888,10 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA12" t="n">
         <v>1.8</v>
@@ -1903,19 +1903,19 @@
         <v>3.01</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
         <v>3.82</v>
@@ -2013,10 +2013,10 @@
         <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AC13" t="n">
         <v>3.84</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45975.375</v>
@@ -781,10 +781,10 @@
         <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>3.48</v>
@@ -820,10 +820,10 @@
         <v>1.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AB3" t="n">
         <v>1.5</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="N4" t="n">
-        <v>4.55</v>
+        <v>3.39</v>
       </c>
       <c r="O4" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="S4" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.37</v>
+        <v>3.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.45</v>
+        <v>6.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45975.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="M5" t="n">
-        <v>2.82</v>
+        <v>3.12</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.64</v>
+        <v>6.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.25</v>
+        <v>2.37</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45975.41666666666</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.06</v>
+        <v>3.45</v>
       </c>
       <c r="R6" t="n">
         <v>1.47</v>
@@ -1171,7 +1171,7 @@
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
         <v>1.39</v>
@@ -1180,13 +1180,13 @@
         <v>2.59</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AD6" t="n">
         <v>1.15</v>
@@ -1198,10 +1198,10 @@
         <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45975.54166666666</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>2.67</v>
@@ -1299,10 +1299,10 @@
         <v>3.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
         <v>3.08</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.29</v>
+        <v>3.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="T8" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.95</v>
+        <v>4.29</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.91</v>
+        <v>3.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>12.16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="T10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
         <v>3.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG10" t="n">
         <v>1.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.6875</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
         <v>2.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.72</v>
+        <v>5.58</v>
       </c>
       <c r="R12" t="n">
         <v>1.33</v>
@@ -1873,7 +1873,7 @@
         <v>2.91</v>
       </c>
       <c r="T12" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U12" t="n">
         <v>1.41</v>
@@ -1885,7 +1885,7 @@
         <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.21</v>
@@ -1894,16 +1894,16 @@
         <v>3.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
         <v>1.81</v>
@@ -1915,7 +1915,7 @@
         <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="R13" t="n">
         <v>1.43</v>
@@ -1995,7 +1995,7 @@
         <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
         <v>8.300000000000001</v>
@@ -2004,37 +2004,37 @@
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
         <v>3.84</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.86</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.95</v>
+        <v>4.29</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.91</v>
+        <v>3.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="P9" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.29</v>
+        <v>3.76</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="T9" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
         <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.69791666666</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -659,40 +659,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.06</v>
@@ -716,16 +716,16 @@
         <v>1.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45975.375</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
         <v>3.42</v>
       </c>
       <c r="U3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="V3" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
         <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD3" t="n">
         <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
         <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45975.39583333334</v>
@@ -906,25 +906,25 @@
         <v>3.39</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
         <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.64</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -933,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
         <v>1.7</v>
@@ -948,22 +948,22 @@
         <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE4" t="n">
         <v>2.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45975.41666666666</v>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.16</v>
+        <v>5.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
         <v>2.29</v>
@@ -1043,40 +1043,40 @@
         <v>3.42</v>
       </c>
       <c r="U5" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="V5" t="n">
         <v>8.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AB5" t="n">
         <v>1.51</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
@@ -1144,13 +1144,13 @@
         <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="P6" t="n">
         <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="R6" t="n">
         <v>1.47</v>
@@ -1159,7 +1159,7 @@
         <v>2.39</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
         <v>1.26</v>
@@ -1201,7 +1201,7 @@
         <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45975.54166666666</v>
@@ -1263,31 +1263,31 @@
         <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.04</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
         <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
         <v>7.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
@@ -1296,7 +1296,7 @@
         <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AA7" t="n">
         <v>1.83</v>
@@ -1308,7 +1308,7 @@
         <v>3.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
         <v>1.7</v>
@@ -1317,10 +1317,10 @@
         <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45975.64583333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="N8" t="n">
-        <v>3.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>2.82</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.29</v>
+        <v>10.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2.5</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>4.16</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1501,34 +1501,34 @@
         <v>3.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.45</v>
@@ -1546,19 +1546,19 @@
         <v>4.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>9.800000000000001</v>
+        <v>3.18</v>
       </c>
       <c r="O10" t="n">
-        <v>1.66</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>2.54</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>3.19</v>
       </c>
       <c r="U10" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.62</v>
+        <v>3.98</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.82</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N13" t="n">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
         <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
@@ -2007,25 +2007,25 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC13" t="n">
         <v>3.84</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AF13" t="n">
         <v>1.86</v>
@@ -2034,7 +2034,7 @@
         <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>9.800000000000001</v>
+        <v>3.18</v>
       </c>
       <c r="O8" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.25</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.98</v>
+        <v>2.57</v>
       </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.58</v>
+        <v>2.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.72</v>
+        <v>3.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.16</v>
+        <v>1.62</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>1.24</v>
       </c>
       <c r="M9" t="n">
-        <v>3.07</v>
+        <v>5.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>2.99</v>
+        <v>1.67</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>10.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE9" t="n">
         <v>2.5</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="AF9" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.61</v>
+        <v>4.16</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.2</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.19</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
         <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.6875</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -668,64 +668,64 @@
         <v>3.02</v>
       </c>
       <c r="O2" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
         <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.69</v>
+        <v>3.08</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45975.375</v>
@@ -764,39 +764,39 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="M3" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="N3" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="P3" t="n">
         <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
         <v>2.31</v>
@@ -808,19 +808,19 @@
         <v>1.23</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
         <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AA3" t="n">
         <v>2.5</v>
@@ -829,22 +829,22 @@
         <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG3" t="n">
         <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45975.39583333334</v>
@@ -893,77 +893,77 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.55</v>
+        <v>6.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
         <v>2.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG4" t="n">
         <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45975.41666666666</v>
@@ -999,24 +999,24 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="M5" t="n">
         <v>3.15</v>
@@ -1028,16 +1028,16 @@
         <v>2.42</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
         <v>3.42</v>
@@ -1055,22 +1055,22 @@
         <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
         <v>2.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE5" t="n">
         <v>2.15</v>
@@ -1079,10 +1079,10 @@
         <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45975.41666666666</v>
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
         <v>3.86</v>
@@ -1165,10 +1165,10 @@
         <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.07</v>
@@ -1177,13 +1177,13 @@
         <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
         <v>4.3</v>
@@ -1192,16 +1192,16 @@
         <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45975.54166666666</v>
@@ -1263,40 +1263,40 @@
         <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="P7" t="n">
         <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.9</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
         <v>7.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="AA7" t="n">
         <v>1.83</v>
@@ -1305,19 +1305,19 @@
         <v>1.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
         <v>1.67</v>
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
@@ -1412,34 +1412,34 @@
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
         <v>2.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
         <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45975.6875</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.24</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>5.2</v>
+        <v>3.07</v>
       </c>
       <c r="N9" t="n">
-        <v>9.800000000000001</v>
+        <v>3.32</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67</v>
+        <v>2.99</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.25</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.98</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>2.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.72</v>
+        <v>4.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.16</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.25</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="AF10" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1977,40 +1977,40 @@
         <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="T13" t="n">
         <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AA13" t="n">
         <v>2.12</v>
@@ -2019,22 +2019,22 @@
         <v>1.64</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>

--- a/jogos_2025-11-14.xlsx
+++ b/jogos_2025-11-14.xlsx
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="M7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.3</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.6</v>
-      </c>
       <c r="O7" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="R7" t="n">
         <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
         <v>7.1</v>
@@ -1290,37 +1290,37 @@
         <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AF7" t="n">
         <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45975.64583333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE9" t="n">
         <v>2.25</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V9" t="n">
-        <v>11</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="AF9" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45975.6875</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.25</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V10" t="n">
-        <v>5.85</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.72</v>
+        <v>4.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45975.6875</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>2.06</v>
       </c>
       <c r="P11" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.4</v>
+        <v>5.65</v>
       </c>
       <c r="R11" t="n">
         <v>1.33</v>
@@ -1754,7 +1754,7 @@
         <v>2.91</v>
       </c>
       <c r="T11" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="U11" t="n">
         <v>1.41</v>
@@ -1763,22 +1763,22 @@
         <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
@@ -1787,16 +1787,16 @@
         <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45975.69791666666</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.51</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.48</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.32</v>
-      </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>2.42</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45975.83333333334</v>
